--- a/unduhan/latihan-12-pembersihan-kontak-kunci.xlsx
+++ b/unduhan/latihan-12-pembersihan-kontak-kunci.xlsx
@@ -28,7 +28,7 @@
     <t xml:space="preserve">Kunci Jawaban: Pembersihan Data Kontak Pelanggan</t>
   </si>
   <si>
-    <t xml:space="preserve">Latihan 12 dari 24  |  Tingkat: Menengah  |  Perkiraan waktu: 50 menit  |  pushexcel.github.io/Pushexcel</t>
+    <t xml:space="preserve">Latihan 12 dari 104  |  Tingkat: Menengah  |  Perkiraan waktu: 50 menit  |  pushexcel.github.io/Pushexcel</t>
   </si>
   <si>
     <t xml:space="preserve">Skenario</t>
